--- a/output/tables/afs_hist_compliance_table.xlsx
+++ b/output/tables/afs_hist_compliance_table.xlsx
@@ -73,7 +73,7 @@
 Compliance status at the given date.</t>
   </si>
   <si>
-    <t xml:space="preserve">Status code: C</t>
+    <t xml:space="preserve">C - In Compliance With Procedural Requirements</t>
   </si>
   <si>
     <t xml:space="preserve">3 - In Compliance, Inspection</t>
@@ -88,7 +88,7 @@
     <t xml:space="preserve">0 - Unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">Status code: P</t>
+    <t xml:space="preserve">P - Present, See Other Program(s)</t>
   </si>
   <si>
     <t xml:space="preserve">8 - No Applicable State Regulation</t>
@@ -103,25 +103,25 @@
     <t xml:space="preserve">H - In Compliance (auto)</t>
   </si>
   <si>
-    <t xml:space="preserve">Status code: B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status code: W</t>
+    <t xml:space="preserve">B - In Violation re Both Emissions and Procedural Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W - In Violation re Procedural Compliance</t>
   </si>
   <si>
     <t xml:space="preserve">2 - In Compliance, Source Test</t>
   </si>
   <si>
-    <t xml:space="preserve">Status code: U</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status code: A</t>
+    <t xml:space="preserve">U - Unknown by Evaluation Calculation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A - Unknown re Procedural Compliance</t>
   </si>
   <si>
     <t xml:space="preserve">7 - In Violation, Unknown re Schedule</t>
   </si>
   <si>
-    <t xml:space="preserve">Status code: Y</t>
+    <t xml:space="preserve">Y - Unknown re Both Emissions and Procedural Compliance</t>
   </si>
   <si>
     <t xml:space="preserve">G - FRV On Schedule (auto)</t>
